--- a/students_graded.xlsx
+++ b/students_graded.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erfanarvan/Desktop/comprehensibilityProject/replication/on-the-reliability-of-code-comprehension-proxies-replication/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erfanarvan/Desktop/comprehensibilityProject/replicationNew/on-the-reliability-of-code-comprehension-proxies-replication/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E863036-8731-B14E-A62B-81425405DFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8381B2D9-0180-6742-A88C-75E49CA176E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
